--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:45:57+02:00</t>
+    <t>2026-06-15T17:08:58+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:08:58+02:00</t>
+    <t>2026-06-16T13:04:47+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:04:47+02:00</t>
+    <t>2026-06-17T15:03:17+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:03:17+02:00</t>
+    <t>2026-06-19T11:56:12+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T11:56:12+02:00</t>
+    <t>2026-06-30T11:44:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T11:44:07+02:00</t>
+    <t>2026-06-30T15:39:02+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
+++ b/site/CodeSystem-KBV-CS-MIO-LAB-QuantityComparator-German.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T15:39:02+02:00</t>
+    <t>2026-07-03T08:43:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
